--- a/www/download/COUNTRY.BGR.rpO2.xlsx
+++ b/www/download/COUNTRY.BGR.rpO2.xlsx
@@ -342,7 +342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>Bulgaria</t>
         </is>
       </c>
     </row>
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Ochoa 2</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -847,2523 +852,4084 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>exchange.r.us</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>0.0671456399048756</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>0.129019769453539</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>1.55465380102638</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>1.75697525069061</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>1.83398739185676</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>2.11747769546194</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>2.18321545619096</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>2.0705219732609</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>1.72965500230581</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>1.5735146527652</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>1.57168460694959</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>1.55789934671618</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>1.42700168561391</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>1.33054449933994</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>1.4031148969898</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>3.519</t>
+          <t>-0.299944840000792</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>3.614</t>
+          <t>-0.16979990232684</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>0.206967795306876</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>3.472</t>
+          <t>-0.0981888255536184</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>3.312</t>
+          <t>-0.232753835601607</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>3.239</t>
+          <t>-0.346998549026545</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>3.215</t>
+          <t>-0.431819147437657</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>3.222</t>
+          <t>-0.507956612242533</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>3.317</t>
+          <t>-0.473747946456234</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>3.404</t>
+          <t>-0.6258446106115</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>3.495</t>
+          <t>-0.657676878070561</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>3.612</t>
+          <t>-0.702018591928059</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>3.727</t>
+          <t>-0.664951648126149</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>3.76</t>
+          <t>-0.613221551327951</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>3.74</t>
+          <t>-0.547892171166248</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2.713</t>
+          <t>0.151166469726977</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2.733</t>
+          <t>0.363702324266511</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2.59</t>
+          <t>1.00060694814924</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2.528</t>
+          <t>0.502482497524061</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2.39</t>
+          <t>0.272588615802861</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2.325</t>
+          <t>0.0719389820233354</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2.272</t>
+          <t>-0.0650254782717508</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2.281</t>
+          <t>-0.188829747289739</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2.365</t>
+          <t>-0.0842955474080515</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2.432</t>
+          <t>-0.397844829661593</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2.523</t>
+          <t>-0.440892012732816</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2.631</t>
+          <t>-0.524904307742104</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>2.74</t>
+          <t>-0.469260325059004</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>2.817</t>
+          <t>-0.384506101931383</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2.724</t>
+          <t>-0.287511772161052</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>6025.009</t>
+          <t>0.438109969583534</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>6178.773</t>
+          <t>0.699005482467523</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>5980.411</t>
+          <t>1.47240937406035</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>5727.669</t>
+          <t>0.815900241407095</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>5532.414</t>
+          <t>0.537995496339463</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>5313.109</t>
+          <t>0.301197027502563</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>5310.295</t>
+          <t>0.133271494878156</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>5320.554</t>
+          <t>-0.0173193061290233</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>5442.215</t>
+          <t>-0.312226999983528</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>5662.196</t>
+          <t>-0.278455720328336</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>5797.413</t>
+          <t>-0.334541808424916</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>5998.505</t>
+          <t>-0.427425998876446</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>6165.971</t>
+          <t>-0.373134983660984</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>6241.306</t>
+          <t>-0.29267187630411</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>6207.343</t>
+          <t>-0.170321017938066</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>gross_output.s.mv</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>4763.822</t>
+          <t>43476993247.6867</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>4804.766</t>
+          <t>44827459989.3273</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>4583.11</t>
+          <t>34449334656.4828</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>4317.376</t>
+          <t>31309331393.7428</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>4123.538</t>
+          <t>33800968881.2369</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>3934.009</t>
+          <t>41183188693.1819</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>3898.358</t>
+          <t>53035137409.2544</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>3902.291</t>
+          <t>59019197661.8142</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>4004.834</t>
+          <t>73042493536.9074</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>4138.132</t>
+          <t>92893428605.7119</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>4244.756</t>
+          <t>104874321023.843</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>4411.226</t>
+          <t>133294017047.266</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>4582.662</t>
+          <t>133916824223.377</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>4717.103</t>
+          <t>133879351815.532</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>4560.187</t>
+          <t>92352640033.4873</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>labour_force_value.s.mv</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>15.32</t>
+          <t>7244587132.91932</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>15.16</t>
+          <t>6406687210.59621</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>14.14</t>
+          <t>4327613586.92999</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>13.11</t>
+          <t>5212709455.84297</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>13.5</t>
+          <t>5933318720.33884</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>13.76</t>
+          <t>6799335398.44506</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>13.46</t>
+          <t>9011457252.64496</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>13.88</t>
+          <t>10328873176.8992</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>12.39</t>
+          <t>12121561860.7329</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>17.18</t>
+          <t>13536978627.0777</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>18.13</t>
+          <t>14194324684.7391</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>18.46</t>
+          <t>15770307074.0244</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>19.11</t>
+          <t>15470861316.4409</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>20.79</t>
+          <t>16882437277.8031</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>21.2</t>
+          <t>13909888089.889</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>value.m.mv</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>16.98</t>
+          <t>53689355.4028271</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>17.68</t>
+          <t>49523945.632795</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>16.87</t>
+          <t>49977297.1966779</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>16.02</t>
+          <t>43585374.482809</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>17.47</t>
+          <t>47356144.5723706</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>17.99</t>
+          <t>58659861.6303708</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>18.7</t>
+          <t>70278132.1379299</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>18.62</t>
+          <t>71842385.5712752</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>13.32</t>
+          <t>67434619.2808063</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>19.53</t>
+          <t>64223838.8430573</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>19.74</t>
+          <t>62084790.7328699</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>20.78</t>
+          <t>62507152.1881645</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>46723368.7247178</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>19.75</t>
+          <t>40860310.4824855</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>21.68</t>
+          <t>29857420.1313034</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>gdp.s.du</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>67.69</t>
+          <t>3376.685990276</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>67.16</t>
+          <t>3819.49939869561</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>68.99</t>
+          <t>3812.88114585975</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>70.87</t>
+          <t>3040.97683587977</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>69.03</t>
+          <t>2653.95003864797</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>68.25</t>
+          <t>1953.43643306189</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>67.83</t>
+          <t>2032.52023210969</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>67.5</t>
+          <t>2084.57865666659</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>74.3</t>
+          <t>1964.74618072215</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>63.28</t>
+          <t>2086.59537548386</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>62.12</t>
+          <t>1906.18735312648</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>60.76</t>
+          <t>1889.9033573748</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>60.99</t>
+          <t>2586.83381629398</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>59.46</t>
+          <t>3147.00056277932</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>57.12</t>
+          <t>3495.11114256426</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>gross_output.s.du</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>7.85</t>
+          <t>18227.2130520174</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>7.83</t>
+          <t>19514.848489872</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>7.26</t>
+          <t>14772.812345833</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>6.72</t>
+          <t>13206.0249433025</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>6.88</t>
+          <t>13276.0982277425</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>6.99</t>
+          <t>12757.4842668453</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>6.92</t>
+          <t>15626.7460869806</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>7.24</t>
+          <t>18273.8949340895</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>8.8</t>
+          <t>23122.5727474749</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>9.22</t>
+          <t>31763.8357114598</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>9.74</t>
+          <t>34665.2485700801</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>10.15</t>
+          <t>46692.8511142255</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>10.54</t>
+          <t>59785.2240842123</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>11.51</t>
+          <t>66878.0084838731</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>12.02</t>
+          <t>53281.1379701971</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>surplus_value.empe.r.pc</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>14.94</t>
+          <t>0.262701093893218</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>15.58</t>
+          <t>0.493065461170718</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>14.84</t>
+          <t>1.19139008097145</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>14.1</t>
+          <t>0.614480844734389</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>15.27</t>
+          <t>0.352084159782855</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>15.68</t>
+          <t>0.138273137977847</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>16.31</t>
+          <t>-0.0108573251130638</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>16.24</t>
+          <t>-0.146536860938935</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>16.65</t>
+          <t>-0.306510614784757</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>17.58</t>
+          <t>-0.387051476201445</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>17.9</t>
+          <t>-0.436282258661218</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>18.72</t>
+          <t>-0.516399332298636</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>18.2</t>
+          <t>-0.466138853483784</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>18.44</t>
+          <t>-0.399539379635433</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>20.22</t>
+          <t>-0.301112745489694</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>capital_depreciation.s.us</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>77.21</t>
+          <t>3447.72564488812</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>76.59</t>
+          <t>4056.45139437598</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>3529.51632179635</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>79.18</t>
+          <t>3363.56304269644</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>77.84</t>
+          <t>3536.89036522245</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>77.33</t>
+          <t>3192.59913736407</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>76.76</t>
+          <t>3620.46079664702</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>76.52</t>
+          <t>4158.10523720059</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>74.55</t>
+          <t>5161.27485912345</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>73.21</t>
+          <t>5890.67711845049</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>72.36</t>
+          <t>6688.3511466785</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>71.13</t>
+          <t>8068.78907233715</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>71.26</t>
+          <t>9931.60253167939</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>70.05</t>
+          <t>12849.9641821979</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>67.76</t>
+          <t>11756.8761003702</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>labour_force_value.m.mv</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.0671456399048756</t>
+          <t>2670.11691932021</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>0.129019769453539</t>
+          <t>2344.01131363319</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1.55465380102638</t>
+          <t>1670.81646645153</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>1.75697525069061</t>
+          <t>2061.77043156585</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>1.83398739185676</t>
+          <t>2482.43105831558</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2.11747769546194</t>
+          <t>2923.8165549108</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2.18321545619096</t>
+          <t>3965.78675907449</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2.0705219732609</t>
+          <t>4529.01568749419</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>1.72965500230581</t>
+          <t>5124.96273496231</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>1.5735146527652</t>
+          <t>5566.19186968654</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>1.57168460694959</t>
+          <t>5626.63998285135</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>1.55789934671618</t>
+          <t>5994.03537591199</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>1.42700168561391</t>
+          <t>5645.68161020358</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>1.33054449933994</t>
+          <t>5992.63001483851</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>1.4031148969898</t>
+          <t>5107.3574774698</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Value transfer through trade</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>trade_transfers.s.mv</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>10575427518.0691</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>11967465259.3391</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>6246788855.97018</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>7599224210.09974</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>8398440695.27176</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>12705212654.9189</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>15858987622.8304</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>20250806562.2776</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>23763849622.1527</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>27895224488.5512</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>25714810124.5622</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>30040641322.5259</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>25883003521.6223</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>24607267320.8449</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>26995138486.9234</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Value transfer through trade of productive sectors</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>trade_transfers.p.s.mv</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>9902915762.47545</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>10695336625.4259</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>5671175496.45719</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>7284182667.72492</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>8244844953.59948</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>11859585027.5152</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>11402758201.2661</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>14892770293.5636</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>17906158194.5539</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>20596209041.0973</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>19298703816.5853</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>19158346889.6606</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>17828176207.9718</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>18609281218.6428</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>21163154575.8761</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Value transfer through trade of unproductive sectors</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>trade_transfers.u.s.mv</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.059</t>
+          <t>672511755.593651</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>0.069</t>
+          <t>1272128633.91314</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>0.058</t>
+          <t>575613359.512986</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>0.057</t>
+          <t>315041542.374817</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>0.056</t>
+          <t>153595741.672281</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>845627627.403629</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.052</t>
+          <t>4456229421.56436</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>0.057</t>
+          <t>5358036268.71401</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>0.069</t>
+          <t>5857691427.59881</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0.082</t>
+          <t>7299015447.45387</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>0.095</t>
+          <t>6416106307.97693</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>0.108</t>
+          <t>10882294432.8653</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>0.135</t>
+          <t>8054827313.65045</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>0.171</t>
+          <t>5997986102.2021</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>0.169</t>
+          <t>5831983911.04729</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Working day of employee per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>abstract_labour.empe.m.mv</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>3371.55955484842</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>3499.76233297912</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>3661.41063170565</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>3328.68886800282</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>3356.45571170148</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>3328.10184482989</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>3922.72892290213</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>3865.3479455056</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>3554.10725632005</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0.052</t>
+          <t>3411.78908970388</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>3171.83678245945</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>0.071</t>
+          <t>2898.71951001663</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>0.093</t>
+          <t>3014.0100572888</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>0.111</t>
+          <t>3598.33833632526</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>0.106</t>
+          <t>3569.46704523155</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>abstract_labour.emp.m.mv</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>3129.17619022397</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>3286.89687159317</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>3434.27012673489</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>3067.54609241059</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>3047.08159437565</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>2991.48391176086</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>3454.67837791617</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>3398.80158889431</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>3157.9204103504</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>3078.83445673766</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>2905.57685424474</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>2670.54397042099</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>2778.27933303212</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>0.041</t>
+          <t>3093.73341911536</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>0.039</t>
+          <t>3062.48452340927</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Total exports (USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>exports.s.us</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>-29.99</t>
+          <t>5721.26684707971</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>-16.98</t>
+          <t>7358.52060140411</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>20.7</t>
+          <t>6196.35018071592</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>-9.82</t>
+          <t>5779.99963217886</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-23.28</t>
+          <t>6949.75614597142</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-34.7</t>
+          <t>6339.86696377089</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>-43.18</t>
+          <t>6298.97003500614</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>-50.8</t>
+          <t>7064.93906070471</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>-47.37</t>
+          <t>9391.07357302661</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>-62.58</t>
+          <t>12285.3479543285</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>-65.77</t>
+          <t>10701.9758549452</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>-70.2</t>
+          <t>15598.6154976521</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>-66.5</t>
+          <t>23672.799380887</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>-61.32</t>
+          <t>28533.0144010217</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>-54.79</t>
+          <t>21725.163896309</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Total exports (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>exports.s.mv</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>15.12</t>
+          <t>12023824682.0776</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>36.37</t>
+          <t>13929295492.9944</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>100.06</t>
+          <t>11654652179.3883</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>50.25</t>
+          <t>9669537363.4199</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>27.26</t>
+          <t>11994898070.4064</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>7.19</t>
+          <t>14008601938.4014</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>-6.5</t>
+          <t>16544349041.2086</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>-18.88</t>
+          <t>18426137351.91</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>-8.43</t>
+          <t>24185320099.1269</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>-39.78</t>
+          <t>34842697177.8963</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>-44.09</t>
+          <t>30003599614.7896</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>-52.49</t>
+          <t>47779839783.1648</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>-46.93</t>
+          <t>52214555073.3683</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>-38.45</t>
+          <t>53019685812.2187</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>-28.75</t>
+          <t>26857663765.692</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Total imports (USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>imports.s.us</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>43.81</t>
+          <t>5490.23842158157</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>69.9</t>
+          <t>6176.15579939194</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>147.24</t>
+          <t>5302.77511120537</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>81.59</t>
+          <t>5314.21712516818</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>53.8</t>
+          <t>7204.36396197689</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>30.12</t>
+          <t>6601.36411143601</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>13.33</t>
+          <t>7146.01509412255</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>-1.73</t>
+          <t>7993.22441665403</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>-31.22</t>
+          <t>10928.7375165054</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>-27.85</t>
+          <t>14474.4025210414</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>-33.45</t>
+          <t>14190.5286717511</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>-42.74</t>
+          <t>20576.4268715346</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>-37.31</t>
+          <t>30675.4328324775</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>-29.27</t>
+          <t>37860.2439430891</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>-17.03</t>
+          <t>24912.5895408874</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Total imports (magnitude of value)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>imports.s.mv</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>11010.847</t>
+          <t>21642650755.3106</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>11878.048</t>
+          <t>21201849648.7938</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>12021.646</t>
+          <t>14832600334.3219</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>10652.043</t>
+          <t>15519903961.3979</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>10093.177</t>
+          <t>21648126891.8013</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>9690.314</t>
+          <t>28551644435.1056</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>11106.1</t>
+          <t>38783730677.7852</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>10951.618</t>
+          <t>45376162454.7188</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>10476.085</t>
+          <t>58599637863.591</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>10478.813</t>
+          <t>76640171921.8797</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>10155.572</t>
+          <t>78975278987.2103</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>9646.005</t>
+          <t>108676203969.883</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>10353.536</t>
+          <t>110404925626.024</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>11631.22</t>
+          <t>115236079851.477</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>11452.942</t>
+          <t>64186148602.9527</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Trade balance (USD)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>trade_balance.s.us</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>9147.748</t>
+          <t>231.028425498138</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>9565.603</t>
+          <t>1182.36480201217</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>9483.489</t>
+          <t>893.575069510543</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>8415.82</t>
+          <t>465.782507010675</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>8022.346</t>
+          <t>-254.607816005468</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>7739.501</t>
+          <t>-261.497147665119</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>8913.617</t>
+          <t>-847.045059116402</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>8815.313</t>
+          <t>-928.285355949323</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>8406.174</t>
+          <t>-1537.66394347881</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>8297.471</t>
+          <t>-2189.05456671294</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>8001.593</t>
+          <t>-3488.55281680589</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>7626.531</t>
+          <t>-4977.81137388255</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>8259.292</t>
+          <t>-7002.63345159048</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>10137.239</t>
+          <t>-9327.22954206735</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>9721.443</t>
+          <t>-3187.42564457845</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Trade balance (magnitude of value)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>trade_balance.s.mv</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>43476.993</t>
+          <t>-9618826073.23301</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>44827.46</t>
+          <t>-7272554155.79947</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>34449.335</t>
+          <t>-3177948154.93356</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>31309.331</t>
+          <t>-5850366597.978</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>33800.969</t>
+          <t>-9653228821.39491</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>41183.189</t>
+          <t>-14543042496.7043</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>53035.137</t>
+          <t>-22239381636.5766</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>59019.198</t>
+          <t>-26950025102.8088</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>73042.494</t>
+          <t>-34414317764.4641</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>92893.429</t>
+          <t>-41797474743.9834</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>104874.321</t>
+          <t>-48971679372.4207</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>133294.017</t>
+          <t>-60896364186.7185</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>133916.824</t>
+          <t>-58190370552.6558</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>133879.352</t>
+          <t>-62216394039.258</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>92352.64</t>
+          <t>-37328484837.2607</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>gdp.p.s.us</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>7012.30761</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>6877.74777</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>6270.65211</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>6914.69346</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>6670.10395</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>6416.64399</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>6743.30415</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>7429.86574</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>9358.55309</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0.032</t>
+          <t>11103.62409</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.035</t>
+          <t>11861.38017</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0.047</t>
+          <t>13600.24546</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>17476.37378</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>0.067</t>
+          <t>20824.95179</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>0.053</t>
+          <t>19526.1047</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Rate of profit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>appropriated_profit.r.pc</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>8054.339</t>
+          <t>0.0380771013870919</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>8773.753</t>
+          <t>0.036029677244025</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>8891.416</t>
+          <t>0.0264435587272494</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>7209.66</t>
+          <t>0.0312512803716646</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>6756.961</t>
+          <t>0.0350731110414279</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>6306.004</t>
+          <t>0.0502406308041642</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>6898.108</t>
+          <t>0.0486879810313237</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>6732.564</t>
+          <t>0.050289189476238</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>6206.488</t>
+          <t>0.0481763610183856</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>6102.254</t>
+          <t>0.0528344823709086</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>5766.874</t>
+          <t>0.0477227532527287</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>5395.104</t>
+          <t>0.0467491783259182</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>5794.418</t>
+          <t>0.0501451606622436</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>6299.805</t>
+          <t>0.036373665675204</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>6058.105</t>
+          <t>0.0299956595016292</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>compensation.empe.s.us</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>5489.46630861788</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>5006.89951687757</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>3785.66597417408</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>4945.03266376072</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>4798.34269918028</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>4380.49479616497</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>4758.44007447194</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>5335.1763633511</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>6958.43965857143</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>8259.53538536535</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>9075.80306826029</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>10152.1320669268</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>13383.0860932627</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>17345.3482740352</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>17471.3095980248</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>compensation.emp.s.us</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>7244.587</t>
+          <t>6607.49241501291</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>6406.687</t>
+          <t>6217.29677098901</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>4327.614</t>
+          <t>4798.85981629446</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>5212.709</t>
+          <t>6259.01049800769</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>5933.319</t>
+          <t>6036.95211304725</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>6799.335</t>
+          <t>5484.63915254219</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>9011.457</t>
+          <t>5928.87398593274</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>10328.873</t>
+          <t>6628.1048903259</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>12121.562</t>
+          <t>8671.86455135768</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>13536.979</t>
+          <t>10430.9043908861</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>14194.325</t>
+          <t>11518.9534811051</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>15770.307</t>
+          <t>12840.3745381041</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>15470.861</t>
+          <t>16776.530543474</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>16882.437</t>
+          <t>21718.3063310489</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>13909.888</t>
+          <t>22406.6496559926</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>capital_stock.s.us</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>26.27</t>
+          <t>59355.9918630032</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>49.31</t>
+          <t>69181.360625382</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>119.14</t>
+          <t>57565.0534638733</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>61.45</t>
+          <t>57282.9470666745</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>35.21</t>
+          <t>56099.0221085957</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>13.83</t>
+          <t>49644.40832393</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>-1.09</t>
+          <t>51815.9310363921</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>-14.65</t>
+          <t>56629.2617187464</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>-30.65</t>
+          <t>69005.7104614056</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>-38.71</t>
+          <t>81828.1596914803</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>-43.63</t>
+          <t>94664.9996971436</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>-51.64</t>
+          <t>108329.971368739</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>-46.61</t>
+          <t>134829.532811473</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>-39.95</t>
+          <t>171064.196342325</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>-30.11</t>
+          <t>169178.186375985</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Total real wage (constant USD)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>compensation.emp.s.cu</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>53.689</t>
+          <t>6607.49241501291</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>49.524</t>
+          <t>5584.61395596881</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>49.977</t>
+          <t>5355.12594675398</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>43.585</t>
+          <t>6252.61889475759</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>47.356</t>
+          <t>6075.67002837942</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>58.66</t>
+          <t>5928.32673597345</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>70.278</t>
+          <t>6194.74997422339</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>71.842</t>
+          <t>6389.92025212374</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>67.435</t>
+          <t>6725.03702834154</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>64.224</t>
+          <t>7048.28016969507</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>62.085</t>
+          <t>7484.59364170855</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>62.507</t>
+          <t>7785.80118759571</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>46.723</t>
+          <t>8447.78820222002</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>40.86</t>
+          <t>9793.18926755484</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>29.857</t>
+          <t>11135.2774240175</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>5489.46630861788</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>4474.00496783007</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>4351.7116477922</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>4818.72925768776</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>4544.72734306569</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>4475.68133504424</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>4735.73989088866</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>4844.02819302775</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>5039.88997323793</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>5141.88656144408</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>5458.5149271311</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>5602.33644205346</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>6254.31714764814</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>7238.47960290336</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>7446.98105217487</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>5707.82976498709</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>6549.03348901099</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>5051.74119370554</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>5153.72848199231</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>5504.45759695275</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>5686.76552745781</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>6143.27386406726</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>7005.9449096741</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>8485.71887864231</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>10214.0255791139</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>11206.0255688949</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>13133.1262218959</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>16692.651116526</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>19072.1960689511</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>16831.4873740074</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour (employee only)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>9147748097.54196</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>9565603394.66537</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>9483489488.67567</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>8415819565.6243</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>8022346256.71323</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>7739500840.15192</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>8913616931.51052</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>8815312524.52007</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>8406174482.64817</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>8297471066.15984</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>8001592651.11045</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>7626531030.85376</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>8259291759.9885</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>10137238761.0955</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>9721443497.68812</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>11010847461.4494</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>11878048460.4778</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>12021646108.2215</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>10652043493.3834</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>10093176586.6442</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>9690313835.36697</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>11106100049.3249</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>10951618479.7352</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>10476085169.2964</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>10478813073.5066</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>10155572220.9562</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>9646004821.16061</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>10353535762.4775</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>11631220357.3114</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>11452942465.7701</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>8054339057.74963</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>8773752794.60396</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>8891415901.33083</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>7209660130.43475</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>6756961354.89886</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>6306003561.53269</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>6898108486.37493</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>6732563595.39943</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>6206487564.09396</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>6102254157.91293</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>5766873530.39553</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>5395104482.25452</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>5794417847.85763</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>6299804749.86193</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>6058105241.79902</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Number of persons engaged</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>3518768.77238457</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>3613757.57272251</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>3500495.20410063</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>3472496.63818831</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>3312407.71670649</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>3239300</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>3214800</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>3222200</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>3317400</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>3403500</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>3495200</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>3612000</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>3726600</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>3759606.5276488</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>3739755.21450808</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Number of employee</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>2713209.70272858</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>2733215.13993289</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>2590119.06683022</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2528268.60645396</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>2390124.26970069</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>2325500</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>2272300</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>2280600</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>2365200</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>2432000</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>2522700</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>2631000</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>2740300</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>2817200</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>2723500</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total hours worked by persons engaged</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>6025008671.9305</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>6178772891.40574</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>5980411261.78583</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>5727669207.89169</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>5532413588.31211</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>5313109000</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>5310295000</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>5320554000</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>5442215000</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>5662196000</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>5797413000</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>5998505000</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>6165971000</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>6241305983.29216</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>6207342931.12282</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total hours worked by employees</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>4763821895.65152</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>4804766257.4269</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>4583109986.79267</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>4317376468.78796</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>4123537525.08647</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>3934009000</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>3898358000</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>3902291000</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>4004834000</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>4138132000</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>4244756000</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>4411226000</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>4582661529.17968</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>4717103117.13106</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>4560187201.07867</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Share of high-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>0.153249373821671</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>0.151591592079525</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>0.141357934736138</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>0.131085475404161</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>0.13503866866876</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>0.137628540907754</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>0.134641513454121</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>0.138774875738712</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>0.123858063604186</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>0.171829178515103</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>0.181345393421768</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>0.184575841473869</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>0.19112187778463</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>0.207927195251845</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>0.211989600542139</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Share of medium-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>0.169808085044118</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>0.176824940679784</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>0.168692369777653</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>0.160217209274112</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>0.174665667557867</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>0.179910216418803</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>0.187035676667841</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>0.18621192661329</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>0.133184295915879</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>0.195344038586568</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>0.197423507628787</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>0.207830894374601</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>0.199025936164546</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>0.197474450575818</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>0.216775569682832</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Share of low-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>0.676942541134211</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>0.671583467240692</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>0.689949695486209</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>0.708697315321728</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>0.690295663773374</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>0.682461242673443</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>0.678322809878038</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>0.675013197647998</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>0.742957640479934</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>0.632826782898329</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>0.621231098949445</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>0.607593264151529</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>0.609852186050824</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>0.594598354172337</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>0.57123482977503</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Share of hours worked by high-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>0.0785096043442988</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>0.0783260088229312</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>0.0725635829408859</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>0.0671800623138325</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>0.0688251783923756</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>0.0699078324120806</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>0.0692388796418979</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>0.0724385050920685</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>0.0880048178129122</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>0.0921735966508009</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>0.0974095903387319</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>0.101508629331494</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>0.105364824723641</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>0.115065358467651</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>0.120196730948339</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>0.149374382655247</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>0.155770502716519</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>0.148432965518307</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>0.141043625728438</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>0.152727722560584</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>0.156792418524991</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>0.163142546644421</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>0.162375411188584</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>0.16653267978683</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>0.175757286429952</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>0.179013652283156</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>0.187159780642293</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>0.182028895279162</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>0.18440883981998</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>0.202179913289584</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Share of hours worked by low-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>0.772116013000455</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>0.76590348846055</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>0.779003451540807</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>0.79177631195773</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>0.77844709904704</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>0.773299749062929</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>0.767618573713681</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>0.765186083719348</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>0.745462502400258</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>0.732069116919247</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>0.723576757378112</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>0.711331590026213</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>0.712606279997197</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>0.700525801712369</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>0.677623355762077</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross output (USD)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>28401.43623</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>30820.60983</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>24225.98663</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>25554.54324</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>25628.093</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>25699.58624</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>27780.08002</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>31008.8956</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>40492.17933</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>51515.12221</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>59695.11906</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>71335.35282</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>92537.04128</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>110695.73757</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>106237.58348</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (USD)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>12315.32218</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>12766.33026</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>9850.60101</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>11412.73898</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>11541.40971</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>11171.40468</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>12072.14785</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>13634.0498</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>17157.58343</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>20644.92997</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>22724.97905</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>25973.50076</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>33469.18166</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>40790.5024</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>39238.13703</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>capital_stock.s.cu</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>3985.49606034859</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>3959.94442489811</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>3912.92233580997</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>3897.84900789496</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>3908.98421005755</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>3942.36819554376</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>4007.15957625372</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>4082.12838080333</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>4178.98220818302</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>4301.6328803054</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>4499.12178577914</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>4729.83595275513</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>4992.82783053041</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>5336.88681506164</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>5500.80095714951</t>
         </is>
       </c>
     </row>
@@ -3374,7 +4940,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3397,36 +4963,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Hours of abstract labour</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Hours of abstract labour (employee only)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3438,331 +5019,695 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Total hours worked by persons engaged</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Total hours worked by employees</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Share of hours worked by high-skilled persons engaged</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Share of hours worked by low-skilled persons engaged</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Share of high-skilled labour compensation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Share of medium-skilled labour compensation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Share of low-skilled labour compensation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>compensation.empe.s.us</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>compensation.emp.s.us</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>capital_stock.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>surplus_value.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>surplus_value.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>surplus_value.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Gross output (USD)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>gross_output.s.mv</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Complex labour multiplier</t>
+          <t>Gross Domestic Product (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.emp.r.un</t>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Complex labour multiplier (employee only)</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.empe.r.un</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Gross Domestic Product (USD)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>exchange.r.us</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Complex labour multiplier</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>complex_labour_multiplier.emp.r.un</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Complex labour multiplier (employee only)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>complex_labour_multiplier.empe.r.un</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Working day of employee per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.m.mv</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Magnitude of value "created" by employee in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.m.mv</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Magnitude of value created by persons engaged in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Total exports (USD)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total exports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total imports (USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total imports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>imports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Trade balance (USD)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>trade_balance.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Trade balance (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>trade_balance.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Value transfer through trade</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>trade_transfers.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of productive sectors</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of unproductive sectors</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total real wage (constant USD)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>gdp.p.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Rate of profit</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>appropriated_profit.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3799,6 +5744,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Ochoa 2</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>rpO2</t>
